--- a/samples/sample_import.xlsx
+++ b/samples/sample_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,15 +459,20 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>RoomGroup</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RoomNote</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -481,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4LXS</t>
+          <t>CXJJ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -516,11 +521,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -530,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>QYYT</t>
+          <t>W6M4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,15 +571,16 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+          <t>R02</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>Registration lead</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>负责报到</t>
         </is>
@@ -587,7 +594,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CFNT</t>
+          <t>783C</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -622,11 +629,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>素食 Vegetarian</t>
         </is>
@@ -640,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DFRA</t>
+          <t>2RKR</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -675,11 +683,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -689,7 +698,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M855</t>
+          <t>BNMQ</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -724,11 +733,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>PA team</t>
         </is>
@@ -742,7 +752,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7EKD</t>
+          <t>QDEQ</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -777,11 +787,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -791,7 +802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HGVP</t>
+          <t>4NX6</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,11 +837,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>201</t>
+          <t>R01</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -840,7 +852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DDSL</t>
+          <t>S9ZR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -875,11 +887,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Programme lead</t>
         </is>
@@ -893,7 +906,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q5PT</t>
+          <t>DZ2F</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -928,11 +941,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Peanut allergy</t>
         </is>
@@ -946,7 +960,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>853X</t>
+          <t>8DXF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -981,11 +995,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>R03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -995,7 +1010,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KXQZ</t>
+          <t>G3PV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1030,11 +1045,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>R02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1044,7 +1060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>WBJL</t>
+          <t>3CQ2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1079,11 +1095,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>R04</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/sample_import.xlsx
+++ b/samples/sample_import.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CXJJ</t>
+          <t>4YNQ</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>W6M4</t>
+          <t>HHJ3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>783C</t>
+          <t>VAHA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2RKR</t>
+          <t>PVFD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BNMQ</t>
+          <t>5PXN</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>QDEQ</t>
+          <t>9NCP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4NX6</t>
+          <t>Y9GT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>S9ZR</t>
+          <t>3DS8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DZ2F</t>
+          <t>8BB3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8DXF</t>
+          <t>K4Y5</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>G3PV</t>
+          <t>7NRA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3CQ2</t>
+          <t>EKFB</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/samples/sample_import.xlsx
+++ b/samples/sample_import.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4YNQ</t>
+          <t>5HJB</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HHJ3</t>
+          <t>B8HF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VAHA</t>
+          <t>ESH7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PVFD</t>
+          <t>68Z4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5PXN</t>
+          <t>9CNC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9NCP</t>
+          <t>62VX</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Y9GT</t>
+          <t>455Q</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3DS8</t>
+          <t>VWYN</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>8BB3</t>
+          <t>EQ32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>K4Y5</t>
+          <t>6CUK</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7NRA</t>
+          <t>LUH2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EKFB</t>
+          <t>C8PF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">

--- a/samples/sample_import.xlsx
+++ b/samples/sample_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,40 +439,50 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Emergency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>CampGroup</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>BusTo</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>BusBack</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>RoomGroup</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Room</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>RoomNote</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -486,7 +496,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5HJB</t>
+          <t>QY93</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,34 +509,36 @@
           <t>0123456789</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -536,7 +548,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B8HF</t>
+          <t>7WJ3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -549,38 +561,40 @@
           <t>0129876543</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>后勤 Logistics</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Registration lead</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>负责报到</t>
         </is>
@@ -594,7 +608,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ESH7</t>
+          <t>4ZKC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,34 +621,36 @@
           <t>0111234567</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>弟兄组 Brothers</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>素食 Vegetarian</t>
         </is>
@@ -648,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>68Z4</t>
+          <t>BRLF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -661,34 +677,36 @@
           <t>0162223334</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>姐妹组 Sisters</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -698,7 +716,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>9CNC</t>
+          <t>MWR8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,34 +729,36 @@
           <t>0177778888</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>音响 Audio</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>PA team</t>
         </is>
@@ -752,7 +772,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62VX</t>
+          <t>2DFP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -765,34 +785,36 @@
           <t>0199990000</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -802,7 +824,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>455Q</t>
+          <t>7VFY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,34 +837,36 @@
           <t>0188887777</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>弟兄组 Brothers</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -852,7 +876,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VWYN</t>
+          <t>E3K5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -865,34 +889,36 @@
           <t>0166665555</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>节目 Programme</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>Programme lead</t>
         </is>
@@ -906,7 +932,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EQ32</t>
+          <t>WZNC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -919,34 +945,36 @@
           <t>0155554444</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>Peanut allergy</t>
         </is>
@@ -960,7 +988,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6CUK</t>
+          <t>6N7J</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -973,34 +1001,36 @@
           <t>0144443333</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>姐妹组 Sisters</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1010,7 +1040,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LUH2</t>
+          <t>22ZC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,34 +1053,36 @@
           <t>0133332222</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Organiser</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>接待 Hospitality</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1060,7 +1092,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C8PF</t>
+          <t>XJHV</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1073,34 +1105,36 @@
           <t>0122221111</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Attendee</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/samples/sample_import.xlsx
+++ b/samples/sample_import.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,35 +454,30 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>CampGroup</t>
+          <t>BusTo</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>BusTo</t>
+          <t>BusBack</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>BusBack</t>
+          <t>RoomGroup</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>RoomGroup</t>
+          <t>Room</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Room</t>
+          <t>RoomNote</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>RoomNote</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -496,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>QY93</t>
+          <t>WNRF</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -520,7 +515,11 @@
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -528,17 +527,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
           <t>R01</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -548,7 +542,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7WJ3</t>
+          <t>6FKW</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,7 +566,11 @@
           <t>后勤 Logistics</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>N</t>
@@ -580,21 +578,16 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Registration lead</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
-        <is>
-          <t>Registration lead</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
         <is>
           <t>负责报到</t>
         </is>
@@ -608,7 +601,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4ZKC</t>
+          <t>XMTJ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -632,25 +625,24 @@
           <t>弟兄组 Brothers</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
           <t>R01</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>素食 Vegetarian</t>
         </is>
@@ -664,7 +656,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BRLF</t>
+          <t>CL2W</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -688,25 +680,24 @@
           <t>姐妹组 Sisters</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
           <t>R03</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -716,7 +707,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MWR8</t>
+          <t>UXLR</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -740,7 +731,11 @@
           <t>音响 Audio</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>Y</t>
@@ -748,17 +743,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
           <t>R02</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>PA team</t>
         </is>
@@ -772,7 +762,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2DFP</t>
+          <t>BJ8E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -796,7 +786,11 @@
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>N</t>
@@ -804,17 +798,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
           <t>R03</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -824,7 +813,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7VFY</t>
+          <t>FFSD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -848,7 +837,11 @@
           <t>弟兄组 Brothers</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>Y</t>
@@ -856,17 +849,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
           <t>R01</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -876,7 +864,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>E3K5</t>
+          <t>QWDJ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -900,7 +888,11 @@
           <t>节目 Programme</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>N</t>
@@ -908,17 +900,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
           <t>R04</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Programme lead</t>
         </is>
@@ -932,7 +919,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WZNC</t>
+          <t>ZC8V</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -956,25 +943,24 @@
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
           <t>R04</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Peanut allergy</t>
         </is>
@@ -988,7 +974,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6N7J</t>
+          <t>TTR3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1012,25 +998,24 @@
           <t>姐妹组 Sisters</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
           <t>R03</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1040,7 +1025,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22ZC</t>
+          <t>RHAB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1064,7 +1049,11 @@
           <t>接待 Hospitality</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Y</t>
@@ -1072,17 +1061,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
           <t>R02</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1092,7 +1076,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XJHV</t>
+          <t>LPHE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1116,7 +1100,11 @@
           <t>青年组 Youth</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>N</t>
@@ -1124,17 +1112,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
           <t>R04</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
